--- a/docs/Materials-and-Cost-Table.xlsx
+++ b/docs/Materials-and-Cost-Table.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1332,27 +1332,35 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
-        <v>20</v>
+    <row r="6" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SparkFun M7E Hecto RFID reader</t>
+        </is>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M7E-HECTO module on SparkFun carrier · 902–928 MHz FCC · 0 to +27 dBm · USB-C (CH340C) + 3.3 V UART header · U.FL + on-board PCB antenna · SparkFun WRL-24738</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sparkfun.com/sparkfun-simultaneous-rfid-reader-m7e-hecto.html</t>
+        </is>
       </c>
       <c r="F6" s="2">
-        <v>345</v>
+        <v>309.95</v>
       </c>
       <c r="G6" s="2">
-        <v>345</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>36</v>
+        <v>309.95</v>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The radio. Replaces the M7E-PICO-CB ($345), which has no USB and needed a USB-UART bridge and Molex cable to reach the Pi. Same ThingMagic serial protocol, and +27 dBm rather than +24 dBm.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
@@ -1378,27 +1386,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>22</v>
+    <row r="8" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U.FL to SMA pigtail</t>
+        </is>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>46</v>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 Ω RG178 · 15 cm · U.FL (I-PEX) to SMA male (standard polarity, not RP-SMA)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amazon.com/POBADY-Coaxial-Pigtail-Wireless-Repeater/dp/B09N3L5NQT</t>
+        </is>
       </c>
       <c r="F8" s="2">
-        <v>15.49</v>
+        <v>9.99</v>
       </c>
       <c r="G8" s="2">
-        <v>15.49</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>38</v>
+        <v>9.99</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joins the reader's U.FL port to the antenna's SMA-female. Price is an estimate; confirm at order.</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
@@ -1424,18 +1440,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
-        <v>24</v>
+    <row r="10" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DS3231 RTC</t>
+        </is>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I²C · TCXO ±2 ppm · takes a CR1220 coin cell (not included)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.adafruit.com/product/3013</t>
+        </is>
       </c>
       <c r="F10" s="2">
         <v>17.5</v>
@@ -1443,110 +1465,170 @@
       <c r="G10" s="2">
         <v>17.5</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
-        <v>25</v>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Pi 4 has no battery-backed clock, and offline means no NTP. Adafruit ships the DS3231SN; cheaper modules may carry the ±5 ppm DS3231M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR1220 coin cell</t>
+        </is>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 V lithium · 12 mm</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.adafruit.com/product/380</t>
+        </is>
       </c>
       <c r="F11" s="2">
-        <v>32.5</v>
+        <v>0.95</v>
       </c>
       <c r="G11" s="2">
-        <v>32.5</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>0.95</v>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Battery for the RTC. Out of stock at Adafruit when checked; any CR1220 works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raspberry Pi 4 Model B, 2 GB</t>
+        </is>
       </c>
       <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="1" t="s">
-        <v>27</v>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCM2711 · 4× Cortex-A72 · 2 GB · native Gigabit Ethernet · 2× USB 3.0 + 2× USB 2.0 · 64-bit Raspberry Pi OS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.pishop.us/product/raspberry-pi-4-model-b-2gb/</t>
+        </is>
+      </c>
+      <c r="F12" s="2">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2">
+        <v>55</v>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core compute; runs SplitForge. Ethernet is not on the USB bus as it is on the Pi 3, and the USB ports supply 1.2 A, so the reader needs no powered hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raspberry Pi 15W USB-C power supply</t>
+        </is>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="44">
-        <v>5</v>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1 V · 3 A · US plug · official</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.pishop.us/product/raspberry-pi-15w-power-supply-us-black/</t>
+        </is>
+      </c>
+      <c r="F13" s="2">
+        <v>8.8</v>
       </c>
       <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>8.8</v>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 3 A supply is what lets the Pi 4 give its USB ports 1.2 A; the reader draws over 0.7 A at +27 dBm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-endurance microSD</t>
+        </is>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="17"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 GB · A2 · high-endurance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antenna stand and lane materials</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PVC or light tripod · clamps · zip ties · cones · gaffer tape</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home Depot</t>
+        </is>
+      </c>
+      <c r="F15" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <v>15</v>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antenna placement is the calibration. A read zone you cannot reproduce next weekend is not a measurement.</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="18"/>
@@ -1571,8 +1653,8 @@
         <v>12</v>
       </c>
       <c r="G18" s="34">
-        <f>SUM(G6,G7,G8,G10,G11,G13)</f>
-        <v>484.48</v>
+        <f>SUM(G6,G7,G8,G10,G11,G12,G13,G15)</f>
+        <v>486.18</v>
       </c>
       <c r="H18" s="35"/>
     </row>
@@ -1591,7 +1673,7 @@
       </c>
       <c r="G20" s="27">
         <f>500-G18</f>
-        <v>15.519999999999982</v>
+        <v>13.82</v>
       </c>
       <c r="H20" s="28"/>
     </row>

--- a/docs/Materials-and-Cost-Table.xlsx
+++ b/docs/Materials-and-Cost-Table.xlsx
@@ -1544,19 +1544,23 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 V · 3 A · US plug · official</t>
+          <t xml:space="preserve">5.1 V · 3 A · USB-C · official</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.pishop.us/product/raspberry-pi-15w-power-supply-us-black/</t>
-        </is>
-      </c>
-      <c r="F13" s="2">
-        <v>8.8</v>
-      </c>
-      <c r="G13" s="2">
-        <v>8.8</v>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -1630,14 +1634,40 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="20"/>
+    <row r="16" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USB-C to USB-A cable</t>
+        </is>
+      </c>
+      <c r="C16" s="19">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">≤ 1 ft · data-capable, not charge-only</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joins the reader's USB-C port to the Pi. It is the reader's only data and power link.</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B17" s="21"/>
@@ -1653,8 +1683,8 @@
         <v>12</v>
       </c>
       <c r="G18" s="34">
-        <f>SUM(G6,G7,G8,G10,G11,G12,G13,G15)</f>
-        <v>486.18</v>
+        <f>SUM(G6,G7,G8,G10,G11,G12,G15)</f>
+        <v>477.38</v>
       </c>
       <c r="H18" s="35"/>
     </row>
@@ -1673,7 +1703,7 @@
       </c>
       <c r="G20" s="27">
         <f>500-G18</f>
-        <v>13.82</v>
+        <v>22.62</v>
       </c>
       <c r="H20" s="28"/>
     </row>

--- a/docs/Materials-and-Cost-Table.xlsx
+++ b/docs/Materials-and-Cost-Table.xlsx
@@ -1669,14 +1669,40 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B17" s="21"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
+    <row r="17" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Female-to-female jumper wires</t>
+        </is>
+      </c>
+      <c r="C17" s="22">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.54 mm Dupont · 20 cm</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wire the DS3231's VIN, GND, SDA and SCL to the Pi's GPIO header; the breakout has no plug-in connector.</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F18" s="6" t="s">

--- a/docs/Materials-and-Cost-Table.xlsx
+++ b/docs/Materials-and-Cost-Table.xlsx
@@ -1253,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H22"/>
+  <dimension ref="B2:H23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1670,97 +1670,132 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2.5 screws, nuts and standoffs</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <v>8</v>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2.5 · nylon or brass · 4 for the Pi, 4 for the reader</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mount the Pi 4 (58 × 49 mm hole pattern) and the Hecto (4-40 holes, which M2.5 fits) to the base plate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Female-to-female jumper wires</t>
         </is>
       </c>
-      <c r="C17" s="22">
+      <c r="C18" s="22">
         <v>4</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2.54 mm Dupont · 20 cm</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Wire the DS3231's VIN, GND, SDA and SCL to the Pi's GPIO header; the breakout has no plug-in connector.</t>
         </is>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F18" s="6" t="s">
+    <row r="19" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G19" s="34">
         <f>SUM(G6,G7,G8,G10,G11,G12,G15)</f>
         <v>477.38</v>
       </c>
-      <c r="H18" s="35"/>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F19" s="7" t="s">
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G20" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="20" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F20" s="8" t="s">
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="27">
-        <f>500-G18</f>
+      <c r="G21" s="27">
+        <f>500-G19</f>
         <v>22.62</v>
       </c>
-      <c r="H20" s="28"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F21" s="9" t="s">
+      <c r="H21" s="28"/>
+    </row>
+    <row r="22" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F22" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G22" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="28"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F22" s="10" t="s">
+      <c r="H22" s="28"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="29">
-        <f>G18+G20</f>
+      <c r="G23" s="29">
+        <f>G19+G21</f>
         <v>500</v>
       </c>
-      <c r="H22" s="30"/>
+      <c r="H23" s="30"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G18:H18"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="G4:H4"/>

--- a/docs/Materials-and-Cost-Table.xlsx
+++ b/docs/Materials-and-Cost-Table.xlsx
@@ -1253,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1705,97 +1705,198 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D-printed enclosure</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <v>1</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printed body, panels and base plate</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses the Pi, reader, clock and antenna. Keep metal and cables out of the antenna's path through the front face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling fan</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 V, powered from the Pi's GPIO header</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already have</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moves the Pi's and the reader's heat out through the rear vents; the box is otherwise closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raspberry Pi 4 heatsink set</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium · 3 pieces (CPU, RAM, USB controller) · 3M 8810 thermal tape</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.pishop.us/product/aluminum-heatsink-for-raspberry-pi-4b-3-pack/</t>
+        </is>
+      </c>
+      <c r="F20" s="2">
+        <v>2.95</v>
+      </c>
+      <c r="G20" s="2">
+        <v>2.95</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Pi 4 throttles when hot. The fan only helps if the heat can leave the chips first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Female-to-female jumper wires</t>
         </is>
       </c>
-      <c r="C18" s="22">
+      <c r="C21" s="22">
         <v>4</v>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2.54 mm Dupont · 20 cm</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Already have</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Wire the DS3231's VIN, GND, SDA and SCL to the Pi's GPIO header; the breakout has no plug-in connector.</t>
         </is>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F19" s="6" t="s">
+    <row r="22" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="34">
-        <f>SUM(G6,G7,G8,G10,G11,G12,G15)</f>
-        <v>477.38</v>
-      </c>
-      <c r="H19" s="35"/>
-    </row>
-    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F20" s="7" t="s">
+      <c r="G22" s="34">
+        <f>SUM(G6,G7,G8,G10,G11,G12,G15,G20)</f>
+        <v>480.33</v>
+      </c>
+      <c r="H22" s="35"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G23" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="28"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F21" s="8" t="s">
+      <c r="H23" s="28"/>
+    </row>
+    <row r="24" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="27">
-        <f>500-G19</f>
-        <v>22.62</v>
-      </c>
-      <c r="H21" s="28"/>
-    </row>
-    <row r="22" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F22" s="9" t="s">
+      <c r="G24" s="27">
+        <f>500-G22</f>
+        <v>19.67</v>
+      </c>
+      <c r="H24" s="28"/>
+    </row>
+    <row r="25" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G25" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H22" s="28"/>
-    </row>
-    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F23" s="10" t="s">
+      <c r="H25" s="28"/>
+    </row>
+    <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="29">
-        <f>G19+G21</f>
+      <c r="G26" s="29">
+        <f>G22+G24</f>
         <v>500</v>
       </c>
-      <c r="H23" s="30"/>
+      <c r="H26" s="30"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="G4:H4"/>
